--- a/寵物生活與健康管理/petproject/rag/data/faq_data_expanded.xlsx
+++ b/寵物生活與健康管理/petproject/rag/data/faq_data_expanded.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,16 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>詳細答案</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>回答編號</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>回答內容</t>
         </is>
       </c>
     </row>
@@ -490,6 +500,8 @@
 • 症狀持續超過24小時建議就醫</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -531,6 +543,8 @@
 • 確保環境溫暖，避免感冒</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -566,6 +580,8 @@
 • 建立完整的疫苗記錄</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -601,6 +617,8 @@
 • 保持食碗和水碗清潔</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -636,6 +654,135 @@
 • 避免處罰，專注於正向引導</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>如何在社群中按讚和留言？</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>在毛日好社群中進行互動的步驟：
+按讚功能：
+1. 在社群動態頁面瀏覽貼文
+2. 點擊貼文下方的愛心圖示 ❤️ 即可按讚
+3. 再次點擊可以取消按讚
+4. 按讚數會即時更新顯示
+留言功能：
+1. 點擊貼文下方的留言圖示 💬
+2. 在留言輸入框中寫下你的想法
+3. 點擊「發送」按鈕提交留言
+4. 也可以使用 Ctrl+Enter 快速發送留言
+5. 可以對其他人的留言按讚
+注意事項：
+• 需要登入會員才能按讚和留言
+• 請保持友善的互動環境
+• 可以隨時刪除自己的留言</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>社群功能有哪些？</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>毛日好社群提供以下功能：
+發文功能：
+1. 分享寵物照片和生活動態
+2. 撰寫寵物照護心得
+3. 發布寵物相關問題求助
+互動功能：
+1. 按讚：對喜歡的貼文按讚支持
+2. 留言：與其他寵物家長交流討論
+3. 分享：將實用內容分享給朋友
+瀏覽功能：
+1. 瀏覽其他用戶的寵物動態
+2. 搜尋特定主題的貼文
+3. 查看熱門貼文排行
+個人檔案：
+1. 編輯個人資料和寵物資訊
+2. 查看自己的發文記錄
+3. 管理追蹤和粉絲
+注意事項：
+• 所有功能都需要註冊登入
+• 遵守社群守則，維護友善環境</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>如何發布寵物動態貼文？</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>發布寵物動態貼文的步驟：
+發文步驟：
+1. 進入「毛日好社群」頁面
+2. 在發文區域點擊「分享你的想法...」
+3. 輸入想要分享的內容
+4. 可以上傳寵物照片或影片
+5. 選擇適當的標籤分類
+6. 點擊「發布」按鈕完成
+內容建議：
+• 分享寵物可愛瞬間
+• 記錄寵物成長過程  
+• 分享照護心得和經驗
+• 提問寵物相關疑問
+• 推薦好用的寵物用品
+發文技巧：
+1. 加上相關標籤提高曝光
+2. 搭配清楚的照片更吸引人
+3. 內容真實有趣容易引起共鳴
+注意事項：
+• 確保照片清晰且適當
+• 內容積極正面
+• 尊重其他用戶隱私</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
